--- a/product_selector_out/STM32WB series - diff.xlsx
+++ b/product_selector_out/STM32WB series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +81,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="18">
@@ -1063,18 +1081,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3||5</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1086,59 +1108,67 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3||5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1150,18 +1180,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1173,18 +1203,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1196,18 +1226,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1219,18 +1249,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1242,18 +1272,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1265,76 +1295,88 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3||5</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3||5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1357,7 +1399,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1380,7 +1422,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1403,7 +1445,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1426,7 +1468,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1449,7 +1491,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1469,8 +1511,146 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E54"/>
+  <autoFilter ref="A18:E60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WB series - diff.xlsx
+++ b/product_selector_out/STM32WB series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="18">
@@ -1081,22 +1063,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3||5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1108,67 +1086,59 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3, 5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3||5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1180,18 +1150,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1203,18 +1173,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1226,18 +1196,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1249,18 +1219,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1272,18 +1242,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1295,88 +1265,76 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3||5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>3, 5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3||5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1399,7 +1357,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1422,7 +1380,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1445,7 +1403,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1468,7 +1426,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1491,7 +1449,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1511,146 +1469,8 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E60"/>
+  <autoFilter ref="A18:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WB series - diff.xlsx
+++ b/product_selector_out/STM32WB series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1206</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1170</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="18">
@@ -1150,18 +1150,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1178,13 +1178,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1196,18 +1196,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1224,13 +1224,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1242,18 +1242,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1270,13 +1270,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -1288,18 +1288,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1316,13 +1316,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -1334,18 +1334,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1362,13 +1362,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -1380,18 +1380,18 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1408,13 +1408,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -1426,18 +1426,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1454,13 +1454,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -1469,8 +1469,31 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E54"/>
+  <autoFilter ref="A18:E55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>